--- a/artfynd/A 25768-2024 artfynd.xlsx
+++ b/artfynd/A 25768-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118254684</v>
+        <v>118254614</v>
       </c>
       <c r="B2" t="n">
-        <v>97880</v>
+        <v>97868</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,16 +691,16 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>219874</v>
+        <v>219862</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>721764</v>
+        <v>721762</v>
       </c>
       <c r="R2" t="n">
-        <v>6378619</v>
+        <v>6378623</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118255179</v>
+        <v>118254684</v>
       </c>
       <c r="B4" t="n">
-        <v>97763</v>
+        <v>97880</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>219790</v>
+        <v>219874</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,13 +919,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>721770</v>
+        <v>721764</v>
       </c>
       <c r="R4" t="n">
-        <v>6378576</v>
+        <v>6378619</v>
       </c>
       <c r="S4" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118254614</v>
+        <v>118255179</v>
       </c>
       <c r="B5" t="n">
-        <v>97868</v>
+        <v>97763</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,21 +997,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>219862</v>
+        <v>219790</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,13 +1021,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>721762</v>
+        <v>721770</v>
       </c>
       <c r="R5" t="n">
-        <v>6378623</v>
+        <v>6378576</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
